--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/SOUTH_DAKOTA_2015.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/SOUTH_DAKOTA_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D184"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Escárcega</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -706,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -732,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -747,7 +847,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -789,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -802,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -815,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -828,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -841,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -854,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -885,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -898,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nombre de Dios</t>
+          <t>Nombre De Dios</t>
         </is>
       </c>
       <c r="C39">
@@ -911,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -924,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -939,8 +1099,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estado de México_x000D_
-</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -956,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C43">
@@ -969,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -982,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -995,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1008,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1021,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -1034,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1065,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>San Miguel de Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C51">
@@ -1078,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Atarjea</t>
@@ -1091,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1104,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -1117,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>León</t>
@@ -1130,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -1143,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1156,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Purísima del Rincón</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C58">
@@ -1169,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C59">
@@ -1182,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C60">
@@ -1195,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1215,7 +1464,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C62">
@@ -1226,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1239,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C64">
@@ -1252,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1265,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -1278,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C67">
@@ -1291,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C68">
@@ -1304,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -1317,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C70">
@@ -1330,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C71">
@@ -1343,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C72">
@@ -1356,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -1369,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Xochihuehuetlán</t>
@@ -1382,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1413,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1426,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Molango de Escamilla</t>
+          <t>Molango De Escamilla</t>
         </is>
       </c>
       <c r="C78">
@@ -1439,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C79">
@@ -1452,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zacualtipán de Ángeles</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C80">
@@ -1465,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1496,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Etzatlán</t>
@@ -1509,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Guachinango</t>
@@ -1522,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1535,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Jamay</t>
@@ -1548,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C87">
@@ -1561,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Poncitlán</t>
@@ -1574,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>San Diego de Alejandría</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C89">
@@ -1587,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1600,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C91">
@@ -1613,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Teuchitlán</t>
@@ -1626,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C93">
@@ -1639,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Tototlán</t>
@@ -1652,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -1665,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1696,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Epitacio Huerta</t>
@@ -1709,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -1722,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1735,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1748,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1761,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Queréndaro</t>
@@ -1774,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Tarímbaro</t>
@@ -1787,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1800,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1813,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1826,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1857,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -1870,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -1883,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1914,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -1927,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1940,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1960,7 +2454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C117">
@@ -1971,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -1984,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -1997,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -2010,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>San Juan Quiotepec</t>
@@ -2023,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -2036,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -2049,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -2062,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Zapotitlán Palmas</t>
@@ -2075,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C126">
@@ -2088,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2119,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Coxcatlán</t>
@@ -2132,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -2145,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -2158,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -2171,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -2184,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -2197,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -2210,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -2223,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2243,7 +2832,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C138">
@@ -2254,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2285,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -2298,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -2311,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C143">
@@ -2324,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>San Vicente Tancuayalab</t>
@@ -2337,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -2350,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2381,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2412,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Sahuaripa</t>
@@ -2425,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2456,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -2469,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2500,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Padilla</t>
@@ -2513,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -2526,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2546,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tepetitla de Lardizábal</t>
+          <t>Tepetitla De Lardizábal</t>
         </is>
       </c>
       <c r="C159">
@@ -2557,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2588,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -2601,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Castillo de Teayo</t>
+          <t>Castillo De Teayo</t>
         </is>
       </c>
       <c r="C163">
@@ -2614,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -2627,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Espinal</t>
@@ -2640,9 +3329,14 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C166">
@@ -2653,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C167">
@@ -2666,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -2679,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C169">
@@ -2692,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C170">
@@ -2705,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -2718,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2749,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>General Francisco R. Murguía</t>
@@ -2762,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Luis Moya</t>
@@ -2775,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -2788,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2811,41 +3555,6 @@
       </c>
       <c r="D178">
         <v>1</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
